--- a/www/flightdata/xlsx/eoss-382.xlsx
+++ b/www/flightdata/xlsx/eoss-382.xlsx
@@ -4071,7 +4071,7 @@
         <v>29403.45</v>
       </c>
       <c r="I2">
-        <v>822</v>
+        <v>542</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
